--- a/artfynd/A 21068-2024 artfynd.xlsx
+++ b/artfynd/A 21068-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117365746</v>
       </c>
       <c r="B3" t="n">
-        <v>57203</v>
+        <v>57429</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,12 +890,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21068-2024 artfynd.xlsx
+++ b/artfynd/A 21068-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117365746</v>
       </c>
       <c r="B3" t="n">
-        <v>57429</v>
+        <v>57582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21068-2024 artfynd.xlsx
+++ b/artfynd/A 21068-2024 artfynd.xlsx
@@ -813,11 +813,6 @@
       <c r="B3" t="n">
         <v>57582</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>NT</t>
